--- a/dcf/ROP.xlsx
+++ b/dcf/ROP.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.05497926666008722</v>
+        <v>0.05506699312929968</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.05997926666008722</v>
+        <v>0.06006699312929967</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.06497926666008721</v>
+        <v>0.06506699312929967</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.06997926666008722</v>
+        <v>0.07006699312929968</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.07497926666008722</v>
+        <v>0.07506699312929968</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.07997926666008721</v>
+        <v>0.08006699312929967</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.08497926666008722</v>
+        <v>0.08506699312929968</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>525.9206365227674</v>
+        <v>525.5139960357803</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>503.2784894074447</v>
+        <v>502.8907647177088</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>481.6863079177763</v>
+        <v>481.3165037653632</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>461.088993230926</v>
+        <v>460.7361718150135</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>441.4346197816235</v>
+        <v>441.097897172328</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>422.6742375639798</v>
+        <v>422.3527803544243</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>404.761687639454</v>
+        <v>404.4547098209366</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>564.8563210158439</v>
+        <v>564.4173184854899</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>540.4160484379443</v>
+        <v>539.9976017848061</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>517.1166651507589</v>
+        <v>516.7176888583476</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>494.89807976574</v>
+        <v>494.5175511329123</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>473.7036697783577</v>
+        <v>473.3406249903946</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>453.4800651041147</v>
+        <v>453.1335955671574</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>434.1769460912353</v>
+        <v>433.8461950112766</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>603.7920055089206</v>
+        <v>603.3206409351995</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>577.5536074684437</v>
+        <v>577.1044388519034</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>552.5470223837416</v>
+        <v>552.1188739513321</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>528.7071663005539</v>
+        <v>528.298930450811</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>505.9727197750918</v>
+        <v>505.583352808461</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>484.2858926442496</v>
+        <v>483.9144107798905</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>463.5922045430166</v>
+        <v>463.2376802016165</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>642.7276900019974</v>
+        <v>642.2239633849092</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>614.6911664989432</v>
+        <v>614.2112759190006</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>587.9773796167241</v>
+        <v>587.5200590443164</v>
       </c>
       <c r="E8" s="53" t="n">
-        <v>562.5162528353679</v>
+        <v>562.0803097687095</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>538.2417697718257</v>
+        <v>537.8260806265272</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>515.0917201843845</v>
+        <v>514.6952259926236</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>493.0074629947979</v>
+        <v>492.6291653919564</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>681.6633744950741</v>
+        <v>681.1272858346189</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>651.8287255294429</v>
+        <v>651.318112986098</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>623.4077368497067</v>
+        <v>622.921244137301</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>596.3253393701818</v>
+        <v>595.8616890866082</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>570.5108197685599</v>
+        <v>570.0688084445937</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>545.8975477245192</v>
+        <v>545.4760412053566</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>522.4227214465793</v>
+        <v>522.0206505822963</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>720.5990589881509</v>
+        <v>720.0306082843284</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>688.9662845599424</v>
+        <v>688.4249500531953</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>658.8380940826893</v>
+        <v>658.3224292302855</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>630.134425904996</v>
+        <v>629.6430684045069</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>602.7798697652941</v>
+        <v>602.3115362626602</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>576.7033752646541</v>
+        <v>576.2568564180899</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>551.8379798983606</v>
+        <v>551.4121357726362</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>759.5347434812275</v>
+        <v>758.933930734038</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>726.1038435904418</v>
+        <v>725.5317871202925</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>694.2684513156719</v>
+        <v>693.7236143232699</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>663.9435124398099</v>
+        <v>663.4244477224056</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>635.0489197620282</v>
+        <v>634.5542640807267</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>607.5092028047889</v>
+        <v>607.0376716308228</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>581.2532383501418</v>
+        <v>580.8036209629762</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="54" t="n">
-        <v>364.2000122070312</v>
+        <v>368.625</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.06997926666008722</v>
+        <v>0.07006699312929968</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>1.037737366951215</v>
+        <v>1.03776449388229</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>364.2000122070312</v>
+        <v>368.625</v>
       </c>
     </row>
     <row r="49">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>562.5162528353679</v>
+        <v>562.0803097687095</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>755.9118331760835</v>
+        <v>755.3279504498445</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>408.8148665856202</v>
+        <v>408.4952433150943</v>
       </c>
     </row>
     <row r="59">
